--- a/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:CarePlan</t>
   </si>
   <si>
     <t>ID</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:CarePlan</t>
+    <t>element:CarePlan.activity.detail</t>
   </si>
   <si>
     <t>ID</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-art-regimen-switched-or-substituted.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
